--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484803_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484803_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3732</v>
+        <v>6.6025</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3617</v>
+        <v>4.5381</v>
       </c>
       <c r="F2" t="n">
-        <v>2.0115</v>
+        <v>2.0644</v>
       </c>
       <c r="G2" t="n">
         <v>6.1581</v>
@@ -610,13 +610,13 @@
         <v>3.774</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3886</v>
+        <v>-0.1593</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2199</v>
+        <v>-0.0436</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1687</v>
+        <v>-0.1158</v>
       </c>
       <c r="V2" t="n">
         <v>0.6036</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.719</v>
+        <v>5.0458</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5212</v>
+        <v>4.795</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1979</v>
+        <v>0.2508</v>
       </c>
       <c r="G3" t="n">
         <v>2.4558</v>
@@ -688,13 +688,13 @@
         <v>2.6418</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0576</v>
+        <v>0.2691</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.09</v>
+        <v>0.1838</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0324</v>
+        <v>0.0853</v>
       </c>
       <c r="V3" t="n">
         <v>0.6226</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0399</v>
+        <v>3.8001</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2259</v>
+        <v>2.0125</v>
       </c>
       <c r="F4" t="n">
-        <v>1.814</v>
+        <v>1.7876</v>
       </c>
       <c r="G4" t="n">
         <v>1.9695</v>
@@ -766,13 +766,13 @@
         <v>2.8305</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1834</v>
+        <v>-0.0564</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2997</v>
+        <v>0.0864</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1163</v>
+        <v>-0.1428</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. VERDEGUER FERRER</t>
+          <t>J. MARTIN FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4958</v>
+        <v>3.1039</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2098</v>
+        <v>2.9786</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2859</v>
+        <v>0.1254</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6155</v>
+        <v>0.513</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9117</v>
+        <v>1.015</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7037</v>
+        <v>-0.5021</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6126</v>
+        <v>3.3574</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1731</v>
+        <v>3.2752</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4396</v>
+        <v>0.0823</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9972</v>
+        <v>-2.8445</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2614</v>
+        <v>-2.2601</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7358</v>
+        <v>-0.5843</v>
       </c>
       <c r="P5" t="n">
-        <v>3.3966</v>
+        <v>2.6418</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.3966</v>
+        <v>2.6418</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6913</v>
+        <v>0.5908</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9370000000000001</v>
+        <v>0.2627</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2457</v>
+        <v>0.3281</v>
       </c>
       <c r="V5" t="n">
-        <v>-2.2076</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3398</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.8678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. MARTIN FERNANDEZ</t>
+          <t>L. VERDEGUER FERRER</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.2115</v>
+        <v>2.8377</v>
       </c>
       <c r="E6" t="n">
-        <v>3.1919</v>
+        <v>2.684</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0196</v>
+        <v>0.1537</v>
       </c>
       <c r="G6" t="n">
-        <v>0.513</v>
+        <v>1.6155</v>
       </c>
       <c r="H6" t="n">
-        <v>1.015</v>
+        <v>0.9117</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5021</v>
+        <v>0.7037</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3574</v>
+        <v>2.6126</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2752</v>
+        <v>1.1731</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0823</v>
+        <v>1.4396</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.8445</v>
+        <v>-0.9972</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.2601</v>
+        <v>-0.2614</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5843</v>
+        <v>-0.7358</v>
       </c>
       <c r="P6" t="n">
-        <v>2.6418</v>
+        <v>3.3966</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.6418</v>
+        <v>3.3966</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6983</v>
+        <v>0.0332</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4761</v>
+        <v>0.4111</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2222</v>
+        <v>-0.3779</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-2.2076</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.3398</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.8678</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. BOSCH ROIG</t>
+          <t>M. RODILLA ALCAIDE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6967</v>
+        <v>1.5861</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.366</v>
+        <v>-1.6895</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0627</v>
+        <v>3.2756</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.332</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2027</v>
+        <v>0.9117</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5347</v>
+        <v>-1.5655</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5622</v>
+        <v>-0.0679</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5125999999999999</v>
+        <v>1.1731</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0496</v>
+        <v>-1.241</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8942</v>
+        <v>-0.5859</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3099</v>
+        <v>-0.2614</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5843</v>
+        <v>-0.3245</v>
       </c>
       <c r="P7" t="n">
-        <v>1.887</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9435</v>
+        <v>-3.774</v>
       </c>
       <c r="R7" t="n">
-        <v>2.8305</v>
+        <v>3.5853</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1417</v>
+        <v>-0.0619</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0152</v>
+        <v>-0.0172</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1264</v>
+        <v>-0.0446</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>2.4904</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.1696</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. RODILLA ALCAIDE</t>
+          <t>J. BOSCH ROIG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8696</v>
+        <v>1.5581</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.353</v>
+        <v>-0.3459</v>
       </c>
       <c r="F8" t="n">
-        <v>3.2227</v>
+        <v>1.904</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6536999999999999</v>
+        <v>-0.332</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9117</v>
+        <v>0.2027</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.5655</v>
+        <v>-0.5347</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0679</v>
+        <v>0.5622</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1731</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.241</v>
+        <v>0.0496</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5859</v>
+        <v>-0.8942</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2614</v>
+        <v>-0.3099</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3245</v>
+        <v>-0.5843</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.1887</v>
+        <v>1.887</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.774</v>
+        <v>-0.9435</v>
       </c>
       <c r="R8" t="n">
-        <v>3.5853</v>
+        <v>2.8305</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7783</v>
+        <v>0.0031</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6808</v>
+        <v>0.0354</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0975</v>
+        <v>-0.0323</v>
       </c>
       <c r="V8" t="n">
-        <v>2.4904</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.1696</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. CHOJNACKI</t>
+          <t>V. PELUFO LOZANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3703</v>
+        <v>0.6953</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4833</v>
+        <v>0.144</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.113</v>
+        <v>0.5513</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3381</v>
+        <v>-0.6644</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3381</v>
+        <v>0.3162</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-0.9806</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7184</v>
+        <v>0.4254</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7184</v>
+        <v>0.9516</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.5262</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0565</v>
+        <v>-1.0899</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0565</v>
+        <v>-0.6354</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.4544</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9435</v>
+        <v>2.8305</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9435</v>
+        <v>2.8305</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2352</v>
+        <v>0.416</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2352</v>
+        <v>0.3602</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>0.0559</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-1.8868</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. PELUFO LOZANO</t>
+          <t>M. CHOJNACKI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1211</v>
+        <v>0.6239</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4607</v>
+        <v>0.7369</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3397</v>
+        <v>-0.113</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6644</v>
+        <v>-0.3381</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3162</v>
+        <v>-0.3381</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9806</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4254</v>
+        <v>0.7184</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9516</v>
+        <v>0.7184</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5262</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0899</v>
+        <v>-1.0565</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6354</v>
+        <v>-1.0565</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4544</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.8305</v>
+        <v>0.9435</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.8305</v>
+        <v>0.9435</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4003</v>
+        <v>0.0185</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2446</v>
+        <v>0.0185</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1557</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8868</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5989</v>
+        <v>-0.0794</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4785</v>
+        <v>-0.9325</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8794999999999999</v>
+        <v>0.8531</v>
       </c>
       <c r="G11" t="n">
         <v>-1.7846</v>
@@ -1312,13 +1312,13 @@
         <v>2.2644</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1352</v>
+        <v>0.3843</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1858</v>
+        <v>0.3602</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0506</v>
+        <v>0.0241</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.6251</v>
+        <v>-0.8733</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6418</v>
+        <v>-0.7577</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0167</v>
+        <v>-0.1156</v>
       </c>
       <c r="G12" t="n">
         <v>-4.2201</v>
@@ -1390,13 +1390,13 @@
         <v>3.3966</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8212</v>
+        <v>0.573</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5596</v>
+        <v>0.4436</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2616</v>
+        <v>0.1294</v>
       </c>
       <c r="V12" t="n">
         <v>1.2642</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>23.4309</v>
+        <v>24.9007</v>
       </c>
       <c r="E13" t="n">
-        <v>12.6938</v>
+        <v>14.1635</v>
       </c>
       <c r="F13" t="n">
-        <v>10.7372</v>
+        <v>10.7373</v>
       </c>
       <c r="G13" t="n">
         <v>4.719000000000001</v>
@@ -1438,7 +1438,7 @@
         <v>9.915299999999998</v>
       </c>
       <c r="I13" t="n">
-        <v>-5.1966</v>
+        <v>-5.196599999999999</v>
       </c>
       <c r="J13" t="n">
         <v>21.3287</v>
@@ -1447,7 +1447,7 @@
         <v>21.2238</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1051000000000002</v>
+        <v>0.1050999999999997</v>
       </c>
       <c r="M13" t="n">
         <v>-16.61</v>
@@ -1468,13 +1468,13 @@
         <v>31.1355</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5407000000000002</v>
+        <v>2.0104</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6313000000000002</v>
+        <v>2.1011</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0907</v>
+        <v>-0.09059999999999999</v>
       </c>
       <c r="V13" t="n">
         <v>0.2448000000000004</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P. NAKIDJIM</t>
+          <t>R. MAS GANDIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0216</v>
+        <v>1.9035</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0272</v>
+        <v>1.2935</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0057</v>
+        <v>0.61</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.1196</v>
+        <v>1.1567</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9164</v>
+        <v>0.8969</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2031</v>
+        <v>0.2598</v>
       </c>
       <c r="J14" t="n">
-        <v>1.671</v>
+        <v>1.3523</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5065</v>
+        <v>1.3523</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1645</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.7905</v>
+        <v>-0.1956</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.4229</v>
+        <v>-0.4555</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.3676</v>
+        <v>0.2598</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1887</v>
+        <v>0.1887</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.3209</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1322</v>
+        <v>0.1887</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2091</v>
+        <v>-0.0835</v>
       </c>
       <c r="T14" t="n">
-        <v>1.4319</v>
+        <v>-0.0588</v>
       </c>
       <c r="U14" t="n">
-        <v>1.7772</v>
+        <v>-0.0247</v>
       </c>
       <c r="V14" t="n">
-        <v>1.1207</v>
+        <v>0.6415999999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1245</v>
+        <v>0.6415999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. MAS GANDIA</t>
+          <t>A. VILAGRAN GONZALEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.7977</v>
+        <v>1.3262</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2935</v>
+        <v>1.4146</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5041</v>
+        <v>-0.08840000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>1.1567</v>
+        <v>0.6113</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8969</v>
+        <v>1.4384</v>
       </c>
       <c r="I16" t="n">
-        <v>0.2598</v>
+        <v>-0.8270999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>1.3523</v>
+        <v>2.5792</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3523</v>
+        <v>3.2118</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.6325</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.1956</v>
+        <v>-1.9679</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4555</v>
+        <v>-1.7733</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2598</v>
+        <v>-0.1946</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1887</v>
+        <v>0.5661</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.1322</v>
       </c>
       <c r="R16" t="n">
-        <v>0.1887</v>
+        <v>1.6983</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1893</v>
+        <v>-0.0285</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0588</v>
+        <v>-0.3342</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1305</v>
+        <v>0.3057</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6415999999999999</v>
+        <v>0.1773</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.3018</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6415999999999999</v>
+        <v>-0.1245</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. VILAGRAN GONZALEZ</t>
+          <t>P. NAKIDJIM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6863</v>
+        <v>1.06</v>
       </c>
       <c r="E17" t="n">
-        <v>1.2198</v>
+        <v>2.1503</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5334</v>
+        <v>-1.0903</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6113</v>
+        <v>-1.1196</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4384</v>
+        <v>-0.9164</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8270999999999999</v>
+        <v>-0.2031</v>
       </c>
       <c r="J17" t="n">
-        <v>2.5792</v>
+        <v>1.671</v>
       </c>
       <c r="K17" t="n">
-        <v>3.2118</v>
+        <v>1.5065</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6325</v>
+        <v>0.1645</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.9679</v>
+        <v>-2.7905</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.7733</v>
+        <v>-2.4229</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1946</v>
+        <v>-0.3676</v>
       </c>
       <c r="P17" t="n">
-        <v>0.5661</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1322</v>
+        <v>-1.3209</v>
       </c>
       <c r="R17" t="n">
-        <v>1.6983</v>
+        <v>1.1322</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6684</v>
+        <v>1.2476</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5291</v>
+        <v>0.555</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1393</v>
+        <v>0.6926</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1773</v>
+        <v>1.1207</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3018</v>
+        <v>1.2452</v>
       </c>
       <c r="X17" t="n">
         <v>-0.1245</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3229</v>
+        <v>-0.2171</v>
       </c>
       <c r="E18" t="n">
         <v>-0.1176</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2053</v>
+        <v>-0.09950000000000001</v>
       </c>
       <c r="G18" t="n">
         <v>-0.0329</v>
@@ -1858,13 +1858,13 @@
         <v>0.1887</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1769</v>
+        <v>-0.0711</v>
       </c>
       <c r="T18" t="n">
         <v>-0.1176</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0594</v>
+        <v>0.0465</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3018</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. CABRERA GUEDES</t>
+          <t>I. CAMBRA DOBRE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1269</v>
+        <v>-1.1151</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0977</v>
+        <v>-1.6518</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0292</v>
+        <v>0.5367</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6853</v>
+        <v>-0.2598</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.1553</v>
+        <v>-0.2598</v>
       </c>
       <c r="I19" t="n">
-        <v>0.47</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3728</v>
+        <v>-0.6496</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4962</v>
+        <v>-0.6496</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1234</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3125</v>
+        <v>0.3897</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6591</v>
+        <v>0.3897</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3466</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9435</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.3774</v>
+        <v>-0.9435</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3209</v>
+        <v>0.1887</v>
       </c>
       <c r="S19" t="n">
-        <v>0.86</v>
+        <v>-0.1005</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6525</v>
+        <v>-0.0588</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2076</v>
+        <v>-0.0417</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. CAMBRA DOBRE</t>
+          <t>D. CABRERA GUEDES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1681</v>
+        <v>-1.4564</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.6518</v>
+        <v>-0.6823</v>
       </c>
       <c r="F20" t="n">
-        <v>0.4838</v>
+        <v>-0.7741</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2598</v>
+        <v>-1.6853</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2598</v>
+        <v>-2.1553</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.6496</v>
+        <v>-0.3728</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6496</v>
+        <v>-0.4962</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.1234</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3897</v>
+        <v>-1.3125</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3897</v>
+        <v>-1.6591</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>0.3466</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7548</v>
+        <v>0.9435</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9435</v>
+        <v>-0.3774</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1887</v>
+        <v>1.3209</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.1534</v>
+        <v>0.5305</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0588</v>
+        <v>0.0679</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0946</v>
+        <v>0.4627</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2262</v>
+        <v>-2.3362</v>
       </c>
       <c r="E21" t="n">
         <v>-3.5098</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2835</v>
+        <v>1.1735</v>
       </c>
       <c r="G21" t="n">
         <v>1.1442</v>
@@ -2092,13 +2092,13 @@
         <v>1.3209</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.238</v>
+        <v>-0.348</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2323</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0058</v>
+        <v>-0.1158</v>
       </c>
       <c r="V21" t="n">
         <v>0.6415999999999999</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. BARBERO LOPEZ</t>
+          <t>J. SANTONJA FERRERO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6141</v>
+        <v>-3.1726</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3587</v>
+        <v>-0.9994</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.2555</v>
+        <v>-2.1731</v>
       </c>
       <c r="G22" t="n">
-        <v>-3.4375</v>
+        <v>-1.7296</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.5176</v>
+        <v>-3.0177</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9199000000000001</v>
+        <v>1.2881</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7135</v>
+        <v>1.3007</v>
       </c>
       <c r="K22" t="n">
-        <v>1.807</v>
+        <v>0.576</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.0935</v>
+        <v>0.7248</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.151</v>
+        <v>-3.0303</v>
       </c>
       <c r="N22" t="n">
-        <v>-4.3246</v>
+        <v>-3.5936</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1736</v>
+        <v>0.5633</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.6983</v>
+        <v>-1.887</v>
       </c>
       <c r="Q22" t="n">
         <v>-3.3966</v>
       </c>
       <c r="R22" t="n">
-        <v>1.6983</v>
+        <v>1.5096</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0046</v>
+        <v>-0.0541</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0792</v>
+        <v>-0.1488</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0746</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5171</v>
+        <v>0.4981</v>
       </c>
       <c r="W22" t="n">
         <v>1.2452</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.7281</v>
+        <v>-0.7471</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. SANTONJA FERRERO</t>
+          <t>I. BARBERO LOPEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2648</v>
+        <v>-3.9305</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7789</v>
+        <v>-1.0407</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.4859</v>
+        <v>-2.8898</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.7296</v>
+        <v>-3.4375</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.0177</v>
+        <v>-2.5176</v>
       </c>
       <c r="I23" t="n">
-        <v>1.2881</v>
+        <v>-0.9199000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3007</v>
+        <v>0.7135</v>
       </c>
       <c r="K23" t="n">
-        <v>0.576</v>
+        <v>1.807</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7248</v>
+        <v>-1.0935</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.0303</v>
+        <v>-4.151</v>
       </c>
       <c r="N23" t="n">
-        <v>-3.5936</v>
+        <v>-4.3246</v>
       </c>
       <c r="O23" t="n">
-        <v>0.5633</v>
+        <v>0.1736</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.887</v>
+        <v>-1.6983</v>
       </c>
       <c r="Q23" t="n">
         <v>-3.3966</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5096</v>
+        <v>1.6983</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1463</v>
+        <v>0.6882</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9283</v>
+        <v>0.3972</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.218</v>
+        <v>0.291</v>
       </c>
       <c r="V23" t="n">
-        <v>0.4981</v>
+        <v>0.5171</v>
       </c>
       <c r="W23" t="n">
         <v>1.2452</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.7471</v>
+        <v>-0.7281</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.8694</v>
+        <v>-6.9817</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.2627</v>
+        <v>-5.8729</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.6067</v>
+        <v>-1.1088</v>
       </c>
       <c r="G24" t="n">
         <v>-0.2747</v>
@@ -2326,13 +2326,13 @@
         <v>2.0757</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.726</v>
+        <v>0.1617</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3375</v>
+        <v>0.0522</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3885</v>
+        <v>0.1094</v>
       </c>
       <c r="V24" t="n">
         <v>-0.6415999999999999</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.2119</v>
+        <v>-7.7805</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.3683</v>
+        <v>-3.5888</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.8436</v>
+        <v>-4.1917</v>
       </c>
       <c r="G25" t="n">
         <v>-0.9596</v>
@@ -2404,13 +2404,13 @@
         <v>1.887</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3162</v>
+        <v>0.1152</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8107</v>
+        <v>-0.0312</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5054999999999999</v>
+        <v>0.1464</v>
       </c>
       <c r="V25" t="n">
         <v>-1.6526</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-23.4309</v>
+        <v>-20.8326</v>
       </c>
       <c r="E26" t="n">
-        <v>-10.7372</v>
+        <v>-10.7371</v>
       </c>
       <c r="F26" t="n">
-        <v>-12.6939</v>
+        <v>-10.0955</v>
       </c>
       <c r="G26" t="n">
         <v>-4.719</v>
@@ -2470,7 +2470,7 @@
         <v>-21.2238</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.1051</v>
+        <v>-0.1051000000000001</v>
       </c>
       <c r="P26" t="n">
         <v>-17.9265</v>
@@ -2482,13 +2482,13 @@
         <v>13.209</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.5408000000000002</v>
+        <v>2.0575</v>
       </c>
       <c r="T26" t="n">
-        <v>0.09049999999999969</v>
+        <v>0.0906000000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.6314000000000002</v>
+        <v>1.9668</v>
       </c>
       <c r="V26" t="n">
         <v>-0.2448000000000001</v>
@@ -2497,7 +2497,7 @@
         <v>3.6976</v>
       </c>
       <c r="X26" t="n">
-        <v>-3.942400000000001</v>
+        <v>-3.9424</v>
       </c>
     </row>
   </sheetData>
